--- a/artfynd/A 65319-2021 artfynd.xlsx
+++ b/artfynd/A 65319-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65319-2021 artfynd.xlsx
+++ b/artfynd/A 65319-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98711716</v>
+        <v>98711730</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sydväst Abborrtjärnen, Vrm</t>
+          <t>Syd Abborrtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334169.858478006</v>
+        <v>334264</v>
       </c>
       <c r="R2" t="n">
-        <v>6606031.508709709</v>
+        <v>6605955</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2022-02-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-02-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98711687</v>
+        <v>98711716</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,14 +810,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öster Prästtjärnen, Vrm</t>
+          <t>Sydväst Abborrtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334151.6227950529</v>
+        <v>334170</v>
       </c>
       <c r="R3" t="n">
-        <v>6606044.494573597</v>
+        <v>6606032</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,24 +847,9 @@
           <t>2022-02-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-02-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På en asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,6 +874,436 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>98711687</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Öster Prästtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>334152</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6606044</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-02-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-02-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en asp</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>98711734</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Syd Abborrtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>334264</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6605955</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-02-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-02-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>98711633</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5482</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>101920</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Raggbock</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tragosoma depsarium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Öster Prästtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>333960</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6606140</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-02-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-02-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kläckhål i tallåga på hällmark</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>98711813</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Öst Bredmossetjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>334931</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6605573</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-02-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-02-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ca 20 plantor</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
